--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76D2761E-89BD-4EB6-9D3E-A018713AB346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71B230D-A801-4EEF-B566-6ADED7140804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -705,6 +705,12 @@
       <c r="E3" s="2">
         <v>46202.458333333336</v>
       </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -722,6 +728,12 @@
       <c r="E4" s="2">
         <v>46202.604166666664</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -738,6 +750,12 @@
       </c>
       <c r="E5" s="2">
         <v>46202.791666666664</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71B230D-A801-4EEF-B566-6ADED7140804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F145EF-BD66-44FD-8C01-B9B8A33BF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -774,6 +774,12 @@
       <c r="E6" s="2">
         <v>46203.458333333336</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="1">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F145EF-BD66-44FD-8C01-B9B8A33BF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4471150-1B5D-4F26-B65A-2BF853BB0B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -797,6 +797,12 @@
       <c r="E7" s="2">
         <v>46203.625</v>
       </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -813,6 +819,12 @@
       </c>
       <c r="E8" s="2">
         <v>46203.791666666664</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -830,6 +842,12 @@
       </c>
       <c r="E9" s="2">
         <v>46204.416666666664</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4471150-1B5D-4F26-B65A-2BF853BB0B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857A86F1-2065-4669-A234-3C4F572F8AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -866,6 +866,12 @@
       <c r="E10" s="2">
         <v>46204.583333333336</v>
       </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -883,6 +889,12 @@
       <c r="E11" s="2">
         <v>46204.75</v>
       </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -900,6 +912,12 @@
       <c r="E12" s="2">
         <v>46205.541666666664</v>
       </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -917,6 +935,12 @@
       <c r="E13" s="2">
         <v>46205.708333333336</v>
       </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -933,6 +957,12 @@
       </c>
       <c r="E14" s="2">
         <v>46205.875</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857A86F1-2065-4669-A234-3C4F572F8AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F70BF43-D27D-430F-899E-36448B76C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -162,54 +162,6 @@
   </si>
   <si>
     <t>Octavos de Final</t>
-  </si>
-  <si>
-    <t>Ganador Llave 1</t>
-  </si>
-  <si>
-    <t>Ganador Llave 2</t>
-  </si>
-  <si>
-    <t>Ganador Llave 3</t>
-  </si>
-  <si>
-    <t>Ganador Llave 4</t>
-  </si>
-  <si>
-    <t>Ganador Llave 5</t>
-  </si>
-  <si>
-    <t>Ganador Llave 6</t>
-  </si>
-  <si>
-    <t>Ganador Llave 7</t>
-  </si>
-  <si>
-    <t>Ganador Llave 8</t>
-  </si>
-  <si>
-    <t>Ganador Llave 9</t>
-  </si>
-  <si>
-    <t>Ganador Llave 10</t>
-  </si>
-  <si>
-    <t>Ganador Llave 11</t>
-  </si>
-  <si>
-    <t>Ganador Llave 12</t>
-  </si>
-  <si>
-    <t>Ganador Llave 13</t>
-  </si>
-  <si>
-    <t>Ganador Llave 14</t>
-  </si>
-  <si>
-    <t>Ganador Llave 15</t>
-  </si>
-  <si>
-    <t>Ganador Llave 16</t>
   </si>
   <si>
     <t>Cuartos de Final</t>
@@ -981,6 +933,12 @@
       <c r="E15" s="2">
         <v>46206.5</v>
       </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
@@ -998,6 +956,12 @@
       <c r="E16" s="2">
         <v>46206.666666666664</v>
       </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
@@ -1024,13 +988,13 @@
         <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2">
-        <v>46207.5</v>
+        <v>46207.458333333336</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
@@ -1041,13 +1005,13 @@
         <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2">
-        <v>46207.666666666664</v>
+        <v>46207.625</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
@@ -1058,13 +1022,13 @@
         <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E20" s="2">
-        <v>46208.5</v>
+        <v>46208.583333333336</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
@@ -1075,13 +1039,13 @@
         <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E21" s="2">
-        <v>46208.666666666664</v>
+        <v>46208.75</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
@@ -1092,13 +1056,13 @@
         <v>40</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E22" s="2">
-        <v>46209.5</v>
+        <v>46209.541666666664</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
@@ -1109,13 +1073,13 @@
         <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2">
-        <v>46209.666666666664</v>
+        <v>46209.75</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
@@ -1126,13 +1090,13 @@
         <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
-        <v>46210.5</v>
+        <v>46210.416666666664</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
@@ -1143,13 +1107,13 @@
         <v>40</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2">
-        <v>46210.666666666664</v>
+        <v>46210.583333333336</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -1157,13 +1121,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2">
         <v>46213.5</v>
@@ -1174,13 +1138,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2">
         <v>46213.666666666664</v>
@@ -1191,13 +1155,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E28" s="2">
         <v>46214.5</v>
@@ -1208,13 +1172,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2">
         <v>46214.666666666664</v>
@@ -1225,13 +1189,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2">
         <v>46217.625</v>
@@ -1242,13 +1206,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2">
         <v>46218.625</v>
@@ -1259,13 +1223,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2">
         <v>46222.583333333336</v>

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F70BF43-D27D-430F-899E-36448B76C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0D5DA0-D0D6-4F06-B864-E4A32D61696C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -979,8 +979,14 @@
       <c r="E17" s="2">
         <v>46206.8125</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -997,7 +1003,7 @@
         <v>46207.458333333336</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>46207.625</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1031,7 +1037,7 @@
         <v>46208.583333333336</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1048,7 +1054,7 @@
         <v>46208.75</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>46209.541666666664</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1082,7 +1088,7 @@
         <v>46209.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1099,7 +1105,7 @@
         <v>46210.416666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>46210.583333333336</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1133,7 +1139,7 @@
         <v>46213.5</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1150,7 +1156,7 @@
         <v>46213.666666666664</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1167,7 +1173,7 @@
         <v>46214.5</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1184,7 +1190,7 @@
         <v>46214.666666666664</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1201,7 +1207,7 @@
         <v>46217.625</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1218,7 +1224,7 @@
         <v>46218.625</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>31</v>
       </c>

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0D5DA0-D0D6-4F06-B864-E4A32D61696C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769F6B79-72E3-440D-8044-94EB74AC6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -1002,6 +1002,12 @@
       <c r="E18" s="2">
         <v>46207.458333333336</v>
       </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
@@ -1019,6 +1025,12 @@
       <c r="E19" s="2">
         <v>46207.625</v>
       </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
@@ -1035,6 +1047,12 @@
       </c>
       <c r="E20" s="2">
         <v>46208.583333333336</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769F6B79-72E3-440D-8044-94EB74AC6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F51A122-9CE3-4C6F-ABAB-195BCF97EE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -1071,6 +1071,12 @@
       <c r="E21" s="2">
         <v>46208.75</v>
       </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
@@ -1087,6 +1093,12 @@
       </c>
       <c r="E22" s="2">
         <v>46209.541666666664</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F51A122-9CE3-4C6F-ABAB-195BCF97EE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E622C8C2-A1A9-4323-9244-06C5C362D08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -165,27 +165,6 @@
   </si>
   <si>
     <t>Cuartos de Final</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 1</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 2</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 3</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 4</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 5</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 6</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 7</t>
   </si>
   <si>
     <t>Ganador Octavos 8</t>
@@ -1117,6 +1096,12 @@
       <c r="E23" s="2">
         <v>46209.75</v>
       </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
@@ -1134,6 +1119,12 @@
       <c r="E24" s="2">
         <v>46210.416666666664</v>
       </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
@@ -1160,13 +1151,13 @@
         <v>41</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E26" s="2">
-        <v>46213.5</v>
+        <v>46212.583333333336</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
@@ -1177,13 +1168,13 @@
         <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2">
-        <v>46213.666666666664</v>
+        <v>46213.541666666664</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
@@ -1194,13 +1185,13 @@
         <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E28" s="2">
-        <v>46214.5</v>
+        <v>46214.625</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
@@ -1211,13 +1202,13 @@
         <v>41</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2">
-        <v>46214.666666666664</v>
+        <v>46214.791666666664</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
@@ -1225,16 +1216,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2">
-        <v>46217.625</v>
+        <v>46217.541666666664</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -1242,16 +1233,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E31" s="2">
-        <v>46218.625</v>
+        <v>46218.541666666664</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -1259,16 +1250,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2">
-        <v>46222.583333333336</v>
+        <v>46222.541666666664</v>
       </c>
     </row>
   </sheetData>

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E622C8C2-A1A9-4323-9244-06C5C362D08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D92E7D-9027-4E14-8464-FCED1B2643E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>Cuartos de Final</t>
-  </si>
-  <si>
-    <t>Ganador Octavos 8</t>
   </si>
   <si>
     <t>Semifinal</t>
@@ -1142,6 +1139,12 @@
       <c r="E25" s="2">
         <v>46210.583333333336</v>
       </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
@@ -1205,7 +1208,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2">
         <v>46214.791666666664</v>
@@ -1216,13 +1219,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E30" s="2">
         <v>46217.541666666664</v>
@@ -1233,13 +1236,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E31" s="2">
         <v>46218.541666666664</v>
@@ -1250,13 +1253,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E32" s="2">
         <v>46222.541666666664</v>

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D92E7D-9027-4E14-8464-FCED1B2643E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72115413-AA35-4DC7-9882-CBB4B26CF0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -1208,7 +1208,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2">
         <v>46214.791666666664</v>

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72115413-AA35-4DC7-9882-CBB4B26CF0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955D02F0-DBCF-4693-91D0-5080EB5DE831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -1162,6 +1162,12 @@
       <c r="E26" s="2">
         <v>46212.583333333336</v>
       </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
@@ -1178,6 +1184,12 @@
       </c>
       <c r="E27" s="2">
         <v>46213.541666666664</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955D02F0-DBCF-4693-91D0-5080EB5DE831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9AC6F8-473C-4CA1-A878-29A3756AE63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -168,18 +168,6 @@
   </si>
   <si>
     <t>Semifinal</t>
-  </si>
-  <si>
-    <t>Ganador Cuartos 1</t>
-  </si>
-  <si>
-    <t>Ganador Cuartos 2</t>
-  </si>
-  <si>
-    <t>Ganador Cuartos 3</t>
-  </si>
-  <si>
-    <t>Ganador Cuartos 4</t>
   </si>
   <si>
     <t>Final</t>
@@ -1208,6 +1196,12 @@
       <c r="E28" s="2">
         <v>46214.625</v>
       </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
@@ -1225,6 +1219,12 @@
       <c r="E29" s="2">
         <v>46214.791666666664</v>
       </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
@@ -1234,10 +1234,10 @@
         <v>42</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2">
         <v>46217.541666666664</v>
@@ -1251,10 +1251,10 @@
         <v>42</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E31" s="2">
         <v>46218.541666666664</v>
@@ -1265,13 +1265,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2">
         <v>46222.541666666664</v>

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9AC6F8-473C-4CA1-A878-29A3756AE63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B7B27-A793-48E3-A1F5-20606ABBE8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -1242,6 +1242,12 @@
       <c r="E30" s="2">
         <v>46217.541666666664</v>
       </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="1">

--- a/eliminatorias.xlsx
+++ b/eliminatorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbope\Downloads\Quiniela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B7B27-A793-48E3-A1F5-20606ABBE8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB17777D-CCAD-4479-A449-7D967FE41649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="20777" windowHeight="13200" xr2:uid="{8919F35B-816B-4F9D-87A6-C096CE08113B}"/>
   </bookViews>
@@ -1265,6 +1265,12 @@
       <c r="E31" s="2">
         <v>46218.541666666664</v>
       </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
